--- a/com.sap.integration.dsi/IntegrationFlow/com.sap.integration.dsi.dataplane.generic/Documentation.xlsx
+++ b/com.sap.integration.dsi/IntegrationFlow/com.sap.integration.dsi.dataplane.generic/Documentation.xlsx
@@ -212,7 +212,7 @@
     <t/>
   </si>
   <si>
-    <t>CPI IFlow Version 1.0.5, Figaf revision: 1</t>
+    <t>CPI IFlow Version 1.0.5, Figaf revision: 2</t>
   </si>
   <si>
     <t>Receiver</t>
@@ -419,7 +419,7 @@
     <t>SAP_ProfileId</t>
   </si>
   <si>
-    <t>sampledev(cpi-trial-alex)-&gt;sampleqa(cpi-trial-alex)</t>
+    <t>sampledev(trial-cpi-alex)-&gt;sampleqa(trial-cpi-alex)</t>
   </si>
   <si>
     <t>sampledev</t>
@@ -437,19 +437,19 @@
     <t>onIntegrationFlow</t>
   </si>
   <si>
+    <t>Script Collection</t>
+  </si>
+  <si>
+    <t>com.sap.integration.dsi.dataplane.scripts.txt</t>
+  </si>
+  <si>
+    <t>2026-07-24 20:00 PM</t>
+  </si>
+  <si>
     <t>IFlow Configuration</t>
   </si>
   <si>
     <t>com.sap.integration.dsi.dataplane.generic iflow configuration.json</t>
-  </si>
-  <si>
-    <t>2026-07-13 08:21 AM</t>
-  </si>
-  <si>
-    <t>Script Collection</t>
-  </si>
-  <si>
-    <t>com.sap.integration.dsi.dataplane.scripts.txt</t>
   </si>
 </sst>
 </file>
